--- a/핵심술기 성적 업로드용.xlsx
+++ b/핵심술기 성적 업로드용.xlsx
@@ -20,55 +20,55 @@
     <x:t>12_말초산소포화도 심전도</x:t>
   </x:si>
   <x:si>
+    <x:t>5_피내주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2_경구투약</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9_단순도뇨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3_근육주사</x:t>
+  </x:si>
+  <x:si>
     <x:t>16_통증관리</x:t>
   </x:si>
   <x:si>
+    <x:t>10_유치도뇨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7_수혈요법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11_배출관장</x:t>
+  </x:si>
+  <x:si>
     <x:t>4_피하주사</x:t>
   </x:si>
   <x:si>
-    <x:t>10_유치도뇨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2_경구투약</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14_입원관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9_단순도뇨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7_수혈요법</x:t>
-  </x:si>
-  <x:si>
     <x:t>1_활력징후</x:t>
   </x:si>
   <x:si>
-    <x:t>5_피내주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11_배출관장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3_근육주사</x:t>
-  </x:si>
-  <x:si>
     <x:t>17_욕창관리 및 낙상예방간호</x:t>
   </x:si>
   <x:si>
-    <x:t>15_격리실출입</x:t>
+    <x:t>14_흡인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15_기본 심폐소생술, 제세동기 적용</x:t>
   </x:si>
   <x:si>
     <x:t>8_간헐적 위관영양</x:t>
   </x:si>
   <x:si>
+    <x:t>6_정맥수액주입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13_비강캐뉼라</x:t>
+  </x:si>
+  <x:si>
     <x:t>18_배액관 관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6_정맥수액주입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13_비강캐뉼라</x:t>
   </x:si>
   <x:si>
     <x:t>학번</x:t>
@@ -249,6 +249,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -331,6 +332,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -365,6 +367,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -409,6 +412,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -452,6 +456,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -512,6 +517,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -532,6 +538,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -562,6 +569,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -873,8 +881,7 @@
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.75"/>
   <x:cols>
     <x:col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <x:col min="2" max="2" width="12.77734375" customWidth="1"/>
-    <x:col min="3" max="19" width="12.77734375" customWidth="1"/>
+    <x:col min="2" max="19" width="12.77734375" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -882,7 +889,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1" s="2"/>
       <x:c r="D1" s="2"/>
@@ -965,32 +972,32 @@
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" t="s">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" t="s">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
@@ -1005,17 +1012,17 @@
     </x:row>
     <x:row r="10" spans="1:1">
       <x:c r="A10" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:1">
       <x:c r="A11" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:1">
       <x:c r="A12" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:1">
@@ -1025,12 +1032,12 @@
     </x:row>
     <x:row r="14" spans="1:1">
       <x:c r="A14" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:1">
       <x:c r="A15" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:1">
@@ -1040,17 +1047,17 @@
     </x:row>
     <x:row r="17" spans="1:1">
       <x:c r="A17" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:1">
       <x:c r="A18" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:1">
       <x:c r="A19" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/핵심술기 성적 업로드용.xlsx
+++ b/핵심술기 성적 업로드용.xlsx
@@ -15,66 +15,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <x:si>
     <x:t>12_말초산소포화도 심전도</x:t>
   </x:si>
   <x:si>
+    <x:t>15_기본 심폐소생술, 제세동기 적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8_간헐적 위관영양</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13_비강캐뉼라</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18_배액관 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6_정맥수액주입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학번</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17_욕창관리 및 낙상예방간호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16_통증관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3_근육주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4_피하주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7_수혈요법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1_활력징후</x:t>
+  </x:si>
+  <x:si>
     <x:t>5_피내주사</x:t>
   </x:si>
   <x:si>
+    <x:t>9_단순도뇨</x:t>
+  </x:si>
+  <x:si>
     <x:t>2_경구투약</x:t>
   </x:si>
   <x:si>
-    <x:t>9_단순도뇨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3_근육주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16_통증관리</x:t>
-  </x:si>
-  <x:si>
     <x:t>10_유치도뇨</x:t>
   </x:si>
   <x:si>
-    <x:t>7_수혈요법</x:t>
-  </x:si>
-  <x:si>
     <x:t>11_배출관장</x:t>
   </x:si>
   <x:si>
-    <x:t>4_피하주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1_활력징후</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17_욕창관리 및 낙상예방간호</x:t>
-  </x:si>
-  <x:si>
     <x:t>14_흡인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15_기본 심폐소생술, 제세동기 적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8_간헐적 위관영양</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6_정맥수액주입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13_비강캐뉼라</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18_배액관 관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학번</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목록</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -249,7 +252,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -332,7 +334,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -367,7 +368,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -412,7 +412,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -456,7 +455,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -517,7 +515,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -538,7 +535,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -569,7 +565,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -877,21 +872,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:S1"/>
+  <x:dimension ref="A1:T1"/>
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.75"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <x:col min="2" max="19" width="12.77734375" customWidth="1"/>
+    <x:col min="1" max="2" width="10.5546875" customWidth="1"/>
+    <x:col min="3" max="20" width="12.77734375" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:19">
+    <x:row r="1" spans="1:20">
       <x:c r="A1" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C1" s="2"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
@@ -908,13 +905,11 @@
       <x:c r="Q1" s="2"/>
       <x:c r="R1" s="2"/>
       <x:c r="S1" s="2"/>
+      <x:c r="T1" s="2"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="14">
-    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:F1 B1:B1">
-      <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1">
+    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:G1 C1:C1">
       <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1">
@@ -950,7 +945,10 @@
     <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1">
       <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1 S1:S1">
+    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1">
+      <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1 T1:T1">
       <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -967,62 +965,62 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" t="s">
-        <x:v>2</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" t="s">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" t="s">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" t="s">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:1">
       <x:c r="A9" t="s">
-        <x:v>14</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:1">
       <x:c r="A10" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:1">
       <x:c r="A11" t="s">
-        <x:v>6</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:1">
       <x:c r="A12" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:1">
@@ -1032,32 +1030,32 @@
     </x:row>
     <x:row r="14" spans="1:1">
       <x:c r="A14" t="s">
-        <x:v>16</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:1">
       <x:c r="A15" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:1">
       <x:c r="A16" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:1">
       <x:c r="A17" t="s">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:1">
       <x:c r="A18" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:1">
       <x:c r="A19" t="s">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/핵심술기 성적 업로드용.xlsx
+++ b/핵심술기 성적 업로드용.xlsx
@@ -15,69 +15,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <x:si>
     <x:t>12_말초산소포화도 심전도</x:t>
   </x:si>
   <x:si>
-    <x:t>15_기본 심폐소생술, 제세동기 적용</x:t>
+    <x:t>16_통증관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4_피하주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10_유치도뇨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2_경구투약</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14_입원관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9_단순도뇨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7_수혈요법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1_활력징후</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5_피내주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11_배출관장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3_근육주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17_욕창관리 및 낙상예방간호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15_격리실출입</x:t>
   </x:si>
   <x:si>
     <x:t>8_간헐적 위관영양</x:t>
   </x:si>
   <x:si>
+    <x:t>18_배액관 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6_정맥수액주입</x:t>
+  </x:si>
+  <x:si>
     <x:t>13_비강캐뉼라</x:t>
   </x:si>
   <x:si>
-    <x:t>18_배액관 관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6_정맥수액주입</x:t>
-  </x:si>
-  <x:si>
     <x:t>학번</x:t>
   </x:si>
   <x:si>
     <x:t>목록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17_욕창관리 및 낙상예방간호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16_통증관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3_근육주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4_피하주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7_수혈요법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1_활력징후</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5_피내주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9_단순도뇨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2_경구투약</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10_유치도뇨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11_배출관장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14_흡인</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -872,23 +869,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:T1"/>
+  <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.75"/>
   <x:cols>
-    <x:col min="1" max="2" width="10.5546875" customWidth="1"/>
-    <x:col min="3" max="20" width="12.77734375" customWidth="1"/>
+    <x:col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <x:col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <x:col min="3" max="19" width="12.77734375" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:20">
+    <x:row r="1" spans="1:19">
       <x:c r="A1" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C1" s="2"/>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
@@ -905,11 +901,13 @@
       <x:c r="Q1" s="2"/>
       <x:c r="R1" s="2"/>
       <x:c r="S1" s="2"/>
-      <x:c r="T1" s="2"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="14">
-    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:G1 C1:C1">
+    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:F1 B1:B1">
+      <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1">
       <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1">
@@ -945,10 +943,7 @@
     <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1">
       <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1">
-      <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1 T1:T1">
+    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1 S1:S1">
       <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -965,17 +960,17 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" t="s">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
@@ -985,42 +980,42 @@
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" t="s">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:1">
       <x:c r="A9" t="s">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:1">
       <x:c r="A10" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:1">
       <x:c r="A11" t="s">
-        <x:v>18</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:1">
       <x:c r="A12" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:1">
@@ -1030,32 +1025,32 @@
     </x:row>
     <x:row r="14" spans="1:1">
       <x:c r="A14" t="s">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:1">
       <x:c r="A15" t="s">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:1">
       <x:c r="A16" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:1">
       <x:c r="A17" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:1">
       <x:c r="A18" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:1">
       <x:c r="A19" t="s">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/핵심술기 성적 업로드용.xlsx
+++ b/핵심술기 성적 업로드용.xlsx
@@ -20,61 +20,61 @@
     <x:t>12_말초산소포화도 심전도</x:t>
   </x:si>
   <x:si>
+    <x:t>17_욕창관리 및 낙상예방간호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15_기본 심폐소생술, 제세동기 적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18_배액관 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8_간헐적 위관영양</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6_정맥수액주입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13_비강캐뉼라</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1_활력징후</x:t>
+  </x:si>
+  <x:si>
     <x:t>16_통증관리</x:t>
   </x:si>
   <x:si>
+    <x:t>3_근육주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7_수혈요법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10_유치도뇨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2_경구투약</x:t>
+  </x:si>
+  <x:si>
     <x:t>4_피하주사</x:t>
   </x:si>
   <x:si>
-    <x:t>10_유치도뇨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2_경구투약</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14_입원관리</x:t>
+    <x:t>5_피내주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11_배출관장</x:t>
   </x:si>
   <x:si>
     <x:t>9_단순도뇨</x:t>
   </x:si>
   <x:si>
-    <x:t>7_수혈요법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1_활력징후</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5_피내주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11_배출관장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3_근육주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17_욕창관리 및 낙상예방간호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15_격리실출입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8_간헐적 위관영양</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18_배액관 관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6_정맥수액주입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13_비강캐뉼라</x:t>
+    <x:t>목록</x:t>
   </x:si>
   <x:si>
     <x:t>학번</x:t>
   </x:si>
   <x:si>
-    <x:t>목록</x:t>
+    <x:t>14_흡인</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -249,6 +249,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -331,6 +332,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -365,6 +367,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -409,6 +412,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -452,6 +456,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -512,6 +517,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -532,6 +538,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -562,6 +569,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -873,8 +881,7 @@
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.75"/>
   <x:cols>
     <x:col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <x:col min="2" max="2" width="12.77734375" customWidth="1"/>
-    <x:col min="3" max="19" width="12.77734375" customWidth="1"/>
+    <x:col min="2" max="19" width="12.77734375" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -882,7 +889,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C1" s="2"/>
       <x:c r="D1" s="2"/>
@@ -960,62 +967,62 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" t="s">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" t="s">
-        <x:v>2</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:1">
       <x:c r="A9" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:1">
       <x:c r="A10" t="s">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:1">
       <x:c r="A11" t="s">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:1">
       <x:c r="A12" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:1">
@@ -1025,32 +1032,32 @@
     </x:row>
     <x:row r="14" spans="1:1">
       <x:c r="A14" t="s">
-        <x:v>17</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:1">
       <x:c r="A15" t="s">
-        <x:v>5</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:1">
       <x:c r="A16" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:1">
       <x:c r="A17" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:1">
       <x:c r="A18" t="s">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:1">
       <x:c r="A19" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/핵심술기 성적 업로드용.xlsx
+++ b/핵심술기 성적 업로드용.xlsx
@@ -15,7 +15,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <x:si>
+    <x:t>이름</x:t>
+  </x:si>
   <x:si>
     <x:t>12_말초산소포화도 심전도</x:t>
   </x:si>
@@ -26,6 +29,15 @@
     <x:t>15_기본 심폐소생술, 제세동기 적용</x:t>
   </x:si>
   <x:si>
+    <x:t>학번</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목록</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13_비강캐뉼라</x:t>
+  </x:si>
+  <x:si>
     <x:t>18_배액관 관리</x:t>
   </x:si>
   <x:si>
@@ -35,46 +47,37 @@
     <x:t>6_정맥수액주입</x:t>
   </x:si>
   <x:si>
-    <x:t>13_비강캐뉼라</x:t>
+    <x:t>3_근육주사</x:t>
   </x:si>
   <x:si>
     <x:t>1_활력징후</x:t>
   </x:si>
   <x:si>
+    <x:t>7_수혈요법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2_경구투약</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10_유치도뇨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4_피하주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5_피내주사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9_단순도뇨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11_배출관장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14_흡인</x:t>
+  </x:si>
+  <x:si>
     <x:t>16_통증관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3_근육주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7_수혈요법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10_유치도뇨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2_경구투약</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4_피하주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5_피내주사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11_배출관장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9_단순도뇨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목록</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학번</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14_흡인</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -249,7 +252,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -332,7 +334,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -367,7 +368,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -412,7 +412,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -456,7 +455,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -517,7 +515,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -538,7 +535,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -569,7 +565,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -877,21 +872,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:S1"/>
+  <x:dimension ref="A1:T1"/>
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.75"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <x:col min="2" max="19" width="12.77734375" customWidth="1"/>
+    <x:col min="1" max="2" width="10.5546875" customWidth="1"/>
+    <x:col min="3" max="20" width="12.77734375" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:19">
+    <x:row r="1" spans="1:20">
       <x:c r="A1" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C1" s="2"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
@@ -908,13 +905,11 @@
       <x:c r="Q1" s="2"/>
       <x:c r="R1" s="2"/>
       <x:c r="S1" s="2"/>
+      <x:c r="T1" s="2"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="14">
-    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:F1 B1:B1">
-      <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1">
+    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:G1 C1:C1">
       <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1">
@@ -950,7 +945,10 @@
     <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1">
       <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1 S1:S1">
+    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1">
+      <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1 T1:T1">
       <x:formula1>Sheet2!$A$2:$A$19</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -967,67 +965,67 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:1">
       <x:c r="A9" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:1">
       <x:c r="A10" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:1">
       <x:c r="A11" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:1">
       <x:c r="A12" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:1">
       <x:c r="A13" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:1">
@@ -1042,22 +1040,22 @@
     </x:row>
     <x:row r="16" spans="1:1">
       <x:c r="A16" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:1">
       <x:c r="A17" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:1">
       <x:c r="A18" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:1">
       <x:c r="A19" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
